--- a/BBC_Master.xlsx
+++ b/BBC_Master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\STREAMLT\BSNL_FTTH_Warangal_Dashboard_V5_Pandas_External_Masters\bsnl-ftth-dashboard-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamsh\AppData\Local\Temp\MicrosoftEdgeDownloads\6c7dda8d-47d4-4239-a00f-bdb51e8f6d86\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD33F835-41C2-485E-9CBB-8FAA1686D590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926A485B-46E7-4369-8620-D94021E83722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,9 +58,6 @@
     <t>SPANDANA T</t>
   </si>
   <si>
-    <t>SURENDER G</t>
-  </si>
-  <si>
     <t>KIRAN KUMAR ENUGULA</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>CHR</t>
+  </si>
+  <si>
+    <t>SURENDER GUGULOTH</t>
   </si>
 </sst>
 </file>
@@ -557,10 +557,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="4">
         <v>87</v>
@@ -577,10 +577,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="5">
         <v>40</v>
@@ -597,10 +597,10 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="4">
         <v>64</v>
@@ -617,10 +617,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5">
         <v>34</v>
@@ -637,10 +637,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <v>38</v>
@@ -654,13 +654,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="5">
         <v>47</v>
@@ -674,13 +674,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4">
         <v>40</v>
@@ -694,13 +694,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="5">
         <v>34</v>
@@ -714,13 +714,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="4">
         <v>25</v>
@@ -734,13 +734,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="5">
         <v>44</v>
@@ -754,13 +754,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4">
         <v>17</v>
